--- a/india_compliance/gst_india/data/GSTR1_Excel_Template_V2.1.xlsx
+++ b/india_compliance/gst_india/data/GSTR1_Excel_Template_V2.1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\snv\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EC6A31B1-36B0-4CEF-97A8-B20CD52EC3A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EDE85EF9-4C22-4D8E-9440-CEF5643784EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="12" xr2:uid="{41E52190-9EEB-4DD3-ABBA-4CAF8812DBCA}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="12" activeTab="10" xr2:uid="{41E52190-9EEB-4DD3-ABBA-4CAF8812DBCA}"/>
   </bookViews>
   <sheets>
     <sheet name="b2b,sez,de" sheetId="1" r:id="rId1"/>
@@ -22,8 +22,8 @@
     <sheet name="at" sheetId="8" r:id="rId7"/>
     <sheet name="atadj" sheetId="9" r:id="rId8"/>
     <sheet name="exemp" sheetId="10" r:id="rId9"/>
-    <sheet name="hsn(b2b)" sheetId="11" r:id="rId10"/>
-    <sheet name="hsn(b2c)" sheetId="12" r:id="rId11"/>
+    <sheet name="hsn(b2b)" sheetId="16" r:id="rId10"/>
+    <sheet name="hsn(b2c)" sheetId="11" r:id="rId11"/>
     <sheet name="docs" sheetId="13" r:id="rId12"/>
     <sheet name="eco" sheetId="14" r:id="rId13"/>
     <sheet name="master" sheetId="15" r:id="rId14"/>
@@ -1990,7 +1990,7 @@
       <c r="F5" s="22"/>
     </row>
   </sheetData>
-  <dataValidations count="7">
+  <dataValidations count="8">
     <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="Negative value not allowed. Please enter positive value." sqref="L5:M1048576 E5:E1048576" xr:uid="{2A1457C6-7B6D-4920-82DE-94D7DB82A96C}">
       <formula1>0</formula1>
     </dataValidation>
@@ -2012,6 +2012,9 @@
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I5:I1048576" xr:uid="{A08FA292-14C4-43E2-9ECA-1E6BB0E9AC42}">
       <formula1>INVTYPE</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K5:K1048576" xr:uid="{E7BD63B0-E267-43AB-925E-C4E6A46E022E}">
+      <formula1>RATE</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2019,6 +2022,151 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E8ECCC5-0356-4A61-A052-5D42E87BDC5E}">
+  <dimension ref="A1:K4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="22.5703125" style="24" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.140625" style="19" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.42578125" style="21" customWidth="1"/>
+    <col min="5" max="5" width="23.7109375" style="26" customWidth="1"/>
+    <col min="6" max="6" width="15.28515625" style="21" customWidth="1"/>
+    <col min="7" max="7" width="29.140625" style="26" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21" style="26" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.5703125" style="26" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="20.140625" style="26" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.42578125" style="26" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11">
+      <c r="A1" s="54" t="s">
+        <v>54</v>
+      </c>
+      <c r="B1" s="55"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="57"/>
+      <c r="E1" s="57"/>
+      <c r="F1" s="57"/>
+      <c r="G1" s="57"/>
+      <c r="H1" s="57"/>
+      <c r="I1" s="57"/>
+      <c r="J1" s="57"/>
+      <c r="K1" s="58"/>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="59" t="s">
+        <v>55</v>
+      </c>
+      <c r="B2" s="60"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="62"/>
+      <c r="E2" s="62" t="s">
+        <v>56</v>
+      </c>
+      <c r="F2" s="62"/>
+      <c r="G2" s="62" t="s">
+        <v>4</v>
+      </c>
+      <c r="H2" s="63" t="s">
+        <v>57</v>
+      </c>
+      <c r="I2" s="63" t="s">
+        <v>58</v>
+      </c>
+      <c r="J2" s="63" t="s">
+        <v>59</v>
+      </c>
+      <c r="K2" s="64" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="65">
+        <f ca="1">SUMPRODUCT((A5:A2000&lt;&gt;"")/COUNTIF(A5:A2000,A5:A2000&amp;""))</f>
+        <v>0</v>
+      </c>
+      <c r="B3" s="66"/>
+      <c r="C3" s="67"/>
+      <c r="D3" s="68"/>
+      <c r="E3" s="68">
+        <f ca="1">SUM(E5:E2000)</f>
+        <v>0</v>
+      </c>
+      <c r="F3" s="68"/>
+      <c r="G3" s="68">
+        <f t="shared" ref="G3:K3" ca="1" si="0">SUM(G5:G2000)</f>
+        <v>0</v>
+      </c>
+      <c r="H3" s="68">
+        <f t="shared" ca="1" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I3" s="68">
+        <f t="shared" ca="1" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J3" s="68">
+        <f t="shared" ca="1" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K3" s="69">
+        <f t="shared" ca="1" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" s="70" t="s">
+        <v>60</v>
+      </c>
+      <c r="B4" s="71" t="s">
+        <v>50</v>
+      </c>
+      <c r="C4" s="71" t="s">
+        <v>61</v>
+      </c>
+      <c r="D4" s="72" t="s">
+        <v>62</v>
+      </c>
+      <c r="E4" s="72" t="s">
+        <v>56</v>
+      </c>
+      <c r="F4" s="72" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4" s="72" t="s">
+        <v>17</v>
+      </c>
+      <c r="H4" s="72" t="s">
+        <v>63</v>
+      </c>
+      <c r="I4" s="72" t="s">
+        <v>64</v>
+      </c>
+      <c r="J4" s="72" t="s">
+        <v>65</v>
+      </c>
+      <c r="K4" s="72" t="s">
+        <v>18</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="3">
+    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="Negative value not allowed. Please enter positive value." sqref="E5:E1048576 G5:K1048576" xr:uid="{65F828CA-8475-455D-AAA5-1DF679E75F9B}">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C5:C1048576" xr:uid="{729393FE-03BA-45F4-9E8D-C5FDD8D8C6D4}">
+      <formula1>UQC</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F5:F1048576" xr:uid="{10E13586-4724-4F3F-A1A0-B9D817A4A5CF}">
+      <formula1>RATE</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D8A3D4B-4913-4AC9-8F0A-7D068D18E0EC}">
   <dimension ref="A1:K4"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2157,151 +2305,6 @@
     </dataValidation>
     <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="Negative value not allowed. Please enter positive value." sqref="E5:E1048576 G5:K1048576" xr:uid="{F8911570-8AAA-4508-B273-686D04AE37C3}">
       <formula1>0</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC67EE8A-56AD-40CB-BB94-2B9851B905A3}">
-  <dimension ref="A1:K4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="22.5703125" style="24" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.140625" style="19" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.42578125" style="21" customWidth="1"/>
-    <col min="5" max="5" width="23.7109375" style="26" customWidth="1"/>
-    <col min="6" max="6" width="15.28515625" style="21" customWidth="1"/>
-    <col min="7" max="7" width="29.140625" style="26" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="21" style="26" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.5703125" style="26" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="20.140625" style="26" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.42578125" style="26" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11" ht="15.75" thickBot="1">
-      <c r="A1" s="54" t="s">
-        <v>54</v>
-      </c>
-      <c r="B1" s="55"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="57"/>
-      <c r="E1" s="57"/>
-      <c r="F1" s="57"/>
-      <c r="G1" s="57"/>
-      <c r="H1" s="57"/>
-      <c r="I1" s="57"/>
-      <c r="J1" s="57"/>
-      <c r="K1" s="58"/>
-    </row>
-    <row r="2" spans="1:11" ht="15.75" thickBot="1">
-      <c r="A2" s="59" t="s">
-        <v>55</v>
-      </c>
-      <c r="B2" s="60"/>
-      <c r="C2" s="61"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="62" t="s">
-        <v>56</v>
-      </c>
-      <c r="F2" s="62"/>
-      <c r="G2" s="62" t="s">
-        <v>4</v>
-      </c>
-      <c r="H2" s="63" t="s">
-        <v>57</v>
-      </c>
-      <c r="I2" s="63" t="s">
-        <v>58</v>
-      </c>
-      <c r="J2" s="63" t="s">
-        <v>59</v>
-      </c>
-      <c r="K2" s="64" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" s="65">
-        <f ca="1">SUMPRODUCT((A5:A2000&lt;&gt;"")/COUNTIF(A5:A2000,A5:A2000&amp;""))</f>
-        <v>0</v>
-      </c>
-      <c r="B3" s="66"/>
-      <c r="C3" s="67"/>
-      <c r="D3" s="68"/>
-      <c r="E3" s="68">
-        <f ca="1">SUM(E5:E2000)</f>
-        <v>0</v>
-      </c>
-      <c r="F3" s="68"/>
-      <c r="G3" s="68">
-        <f t="shared" ref="G3:K3" ca="1" si="0">SUM(G5:G2000)</f>
-        <v>0</v>
-      </c>
-      <c r="H3" s="68">
-        <f t="shared" ca="1" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I3" s="68">
-        <f t="shared" ca="1" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J3" s="68">
-        <f t="shared" ca="1" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K3" s="69">
-        <f t="shared" ca="1" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="A4" s="70" t="s">
-        <v>60</v>
-      </c>
-      <c r="B4" s="71" t="s">
-        <v>50</v>
-      </c>
-      <c r="C4" s="71" t="s">
-        <v>61</v>
-      </c>
-      <c r="D4" s="72" t="s">
-        <v>62</v>
-      </c>
-      <c r="E4" s="72" t="s">
-        <v>56</v>
-      </c>
-      <c r="F4" s="72" t="s">
-        <v>16</v>
-      </c>
-      <c r="G4" s="72" t="s">
-        <v>17</v>
-      </c>
-      <c r="H4" s="72" t="s">
-        <v>63</v>
-      </c>
-      <c r="I4" s="72" t="s">
-        <v>64</v>
-      </c>
-      <c r="J4" s="72" t="s">
-        <v>65</v>
-      </c>
-      <c r="K4" s="72" t="s">
-        <v>18</v>
-      </c>
-    </row>
-  </sheetData>
-  <dataValidations count="3">
-    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="Negative value not allowed. Please enter positive value." sqref="E5:E1048576 G5:K1048576" xr:uid="{E4664C93-D428-49B6-9D09-BE7C7B68F3C5}">
-      <formula1>0</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C5:C1048576" xr:uid="{AAC82CD4-B0E3-4740-A7BE-E7B9E8BCAFD3}">
-      <formula1>UQC</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F5:F1048576" xr:uid="{883EEE0E-8CAB-48D7-AD2A-FC6BB12D9C6B}">
-      <formula1>RATE</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4256,7 +4259,7 @@
     <protectedRange sqref="F1:G3" name="Summary_1_1"/>
     <protectedRange sqref="E1:E3" name="Summary_2_1"/>
   </protectedRanges>
-  <dataValidations count="8">
+  <dataValidations count="7">
     <dataValidation type="textLength" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B5:B1048576" xr:uid="{46113DB5-E3D3-4B9F-9B08-60FECA4EB665}">
       <formula1>1</formula1>
       <formula2>16</formula2>
@@ -4276,10 +4279,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G5" xr:uid="{41077115-4EA0-41A6-9A36-5106B5F31F67}">
       <formula1>DIFF</formula1>
     </dataValidation>
-    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J5:J1048576" xr:uid="{9B0C2BBF-78EF-4CC0-B911-242C019C5E63}">
-      <formula1>0</formula1>
-    </dataValidation>
-    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I5:I1048576 F5:F1048576" xr:uid="{8723611B-7202-4F0A-8985-79288E307325}">
+    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I5:J1048576 F5:F1048576" xr:uid="{9B0C2BBF-78EF-4CC0-B911-242C019C5E63}">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>
